--- a/Pareto/Pareto-modelo.xlsx
+++ b/Pareto/Pareto-modelo.xlsx
@@ -22,7 +22,7 @@
     <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Area" vbProcedure="false">Checklist!$B$1:$E$24</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Coleta!$B$1:$F$26</definedName>
     <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Area" vbProcedure="false">'Exemplo 1 - Pizzaria'!$B$1:$L$63</definedName>
-    <definedName function="false" hidden="false" localSheetId="7" name="_xlnm.Print_Area" vbProcedure="false">'Exemplo 2 - Compras'!$B$1:$L$65</definedName>
+    <definedName function="false" hidden="false" localSheetId="7" name="_xlnm.Print_Area" vbProcedure="false">'Exemplo 2 - Compras'!$B$1:$L$66</definedName>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">Folha!$B$1:$L$24</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Instruções!$B$1:$C$41</definedName>
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">Pareto!$B$1:$G$44</definedName>
@@ -173,7 +173,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="223">
   <si>
     <t xml:space="preserve">Pareto e folha de verificação — Como usar esta planilha</t>
   </si>
@@ -760,7 +760,7 @@
     <t xml:space="preserve">Atrasos por 100 entregas, antes e depois</t>
   </si>
   <si>
-    <t xml:space="preserve">Indústria de embalagens plásticas · Suprimentos</t>
+    <t xml:space="preserve">Distribuidora de materiais elétricos · Compras</t>
   </si>
   <si>
     <t xml:space="preserve">Requisições de compra devolvidas ao requisitante, pelo motivo da devolução.</t>
@@ -823,12 +823,15 @@
     <t xml:space="preserve">Por 100 requisições</t>
   </si>
   <si>
-    <t xml:space="preserve">Pareto por área requisitante · as colunas da mesma folha</t>
+    <t xml:space="preserve">Pareto por área requisitante · as colunas da mesma folha, com as requisições de cada área</t>
   </si>
   <si>
     <t xml:space="preserve">Área requisitante</t>
   </si>
   <si>
+    <t xml:space="preserve">Requisições</t>
+  </si>
+  <si>
     <t xml:space="preserve">Devoluções no período</t>
   </si>
   <si>
@@ -836,6 +839,9 @@
   </si>
   <si>
     <t xml:space="preserve">Área com mais devoluções</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Área com a maior taxa de devolução</t>
   </si>
 </sst>
 </file>
@@ -1499,8 +1505,8 @@
         </c:ser>
         <c:gapWidth val="50"/>
         <c:overlap val="0"/>
-        <c:axId val="68123836"/>
-        <c:axId val="84574371"/>
+        <c:axId val="78367281"/>
+        <c:axId val="84703246"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -1745,11 +1751,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="68123836"/>
-        <c:axId val="84574371"/>
+        <c:axId val="78367281"/>
+        <c:axId val="84703246"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="68123836"/>
+        <c:axId val="78367281"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1781,7 +1787,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="84574371"/>
+        <c:crossAx val="84703246"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1789,7 +1795,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="84574371"/>
+        <c:axId val="84703246"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -1830,7 +1836,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="68123836"/>
+        <c:crossAx val="78367281"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="0.2"/>
@@ -2095,11 +2101,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="-10"/>
-        <c:axId val="58446081"/>
-        <c:axId val="36206882"/>
+        <c:axId val="71705992"/>
+        <c:axId val="62767530"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="58446081"/>
+        <c:axId val="71705992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2131,7 +2137,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36206882"/>
+        <c:crossAx val="62767530"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2139,7 +2145,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="36206882"/>
+        <c:axId val="62767530"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2179,7 +2185,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58446081"/>
+        <c:crossAx val="71705992"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2345,8 +2351,8 @@
         </c:ser>
         <c:gapWidth val="50"/>
         <c:overlap val="0"/>
-        <c:axId val="30906876"/>
-        <c:axId val="16806292"/>
+        <c:axId val="47223556"/>
+        <c:axId val="92222937"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2570,11 +2576,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="30906876"/>
-        <c:axId val="16806292"/>
+        <c:axId val="47223556"/>
+        <c:axId val="92222937"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="30906876"/>
+        <c:axId val="47223556"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2606,7 +2612,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="16806292"/>
+        <c:crossAx val="92222937"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2614,7 +2620,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="16806292"/>
+        <c:axId val="92222937"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -2655,7 +2661,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="30906876"/>
+        <c:crossAx val="47223556"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="0.2"/>
@@ -2828,8 +2834,8 @@
         </c:ser>
         <c:gapWidth val="50"/>
         <c:overlap val="0"/>
-        <c:axId val="26886343"/>
-        <c:axId val="15191520"/>
+        <c:axId val="68536233"/>
+        <c:axId val="15037926"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -3065,11 +3071,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="26886343"/>
-        <c:axId val="15191520"/>
+        <c:axId val="68536233"/>
+        <c:axId val="15037926"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="26886343"/>
+        <c:axId val="68536233"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3101,7 +3107,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="15191520"/>
+        <c:crossAx val="15037926"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3109,7 +3115,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="15191520"/>
+        <c:axId val="15037926"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -3150,7 +3156,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26886343"/>
+        <c:crossAx val="68536233"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="0.2"/>
@@ -7339,7 +7345,7 @@
     <tabColor rgb="FF5B6B76"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:L65"/>
+  <dimension ref="B1:L66"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -8027,6 +8033,12 @@
       <c r="I52" s="18" t="s">
         <v>115</v>
       </c>
+      <c r="J52" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="K52" s="18" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="11" t="n">
@@ -8054,6 +8066,13 @@
       <c r="I53" s="31" t="n">
         <v>0.8</v>
       </c>
+      <c r="J53" s="47" t="n">
+        <v>80</v>
+      </c>
+      <c r="K53" s="38" t="n">
+        <f aca="false">100*D53/J53</f>
+        <v>60</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="11" t="n">
@@ -8081,6 +8100,13 @@
       <c r="I54" s="31" t="n">
         <v>0.8</v>
       </c>
+      <c r="J54" s="47" t="n">
+        <v>75</v>
+      </c>
+      <c r="K54" s="38" t="n">
+        <f aca="false">100*D54/J54</f>
+        <v>30.6666666666667</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="11" t="n">
@@ -8108,6 +8134,13 @@
       <c r="I55" s="31" t="n">
         <v>0.8</v>
       </c>
+      <c r="J55" s="47" t="n">
+        <v>35</v>
+      </c>
+      <c r="K55" s="38" t="n">
+        <f aca="false">100*D55/J55</f>
+        <v>31.4285714285714</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="11" t="n">
@@ -8135,6 +8168,13 @@
       <c r="I56" s="31" t="n">
         <v>0.8</v>
       </c>
+      <c r="J56" s="47" t="n">
+        <v>30</v>
+      </c>
+      <c r="K56" s="38" t="n">
+        <f aca="false">100*D56/J56</f>
+        <v>30</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="11" t="n">
@@ -8161,6 +8201,13 @@
       <c r="H57" s="13"/>
       <c r="I57" s="31" t="n">
         <v>0.8</v>
+      </c>
+      <c r="J57" s="47" t="n">
+        <v>30</v>
+      </c>
+      <c r="K57" s="38" t="n">
+        <f aca="false">100*D57/J57</f>
+        <v>30</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8180,6 +8227,14 @@
       <c r="G58" s="6"/>
       <c r="H58" s="6"/>
       <c r="I58" s="6"/>
+      <c r="J58" s="18" t="n">
+        <f aca="false">SUM(J53:J57)</f>
+        <v>250</v>
+      </c>
+      <c r="K58" s="40" t="n">
+        <f aca="false">100*D58/J58</f>
+        <v>40</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="14" t="s">
@@ -8198,7 +8253,7 @@
     </row>
     <row r="61" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B61" s="15" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C61" s="15"/>
       <c r="D61" s="15"/>
@@ -8252,7 +8307,7 @@
     </row>
     <row r="64" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="15" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C64" s="15"/>
       <c r="D64" s="15"/>
@@ -8270,7 +8325,7 @@
     </row>
     <row r="65" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="15" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C65" s="15"/>
       <c r="D65" s="15"/>
@@ -8286,8 +8341,26 @@
       <c r="K65" s="21"/>
       <c r="L65" s="21"/>
     </row>
+    <row r="66" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B66" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="C66" s="15"/>
+      <c r="D66" s="15"/>
+      <c r="E66" s="15"/>
+      <c r="F66" s="21" t="str">
+        <f aca="false">INDEX(C53:C57,MATCH(MAX(K53:K57),K53:K57,0))&amp;" · "&amp;TEXT(MAX(K53:K57),"0,0")&amp;" por 100 requisições"</f>
+        <v>Manutenção · 60,0 por 100 requisições</v>
+      </c>
+      <c r="G66" s="21"/>
+      <c r="H66" s="21"/>
+      <c r="I66" s="21"/>
+      <c r="J66" s="21"/>
+      <c r="K66" s="21"/>
+      <c r="L66" s="21"/>
+    </row>
   </sheetData>
-  <mergeCells count="62">
+  <mergeCells count="64">
     <mergeCell ref="B1:L1"/>
     <mergeCell ref="B2:L2"/>
     <mergeCell ref="B4:C4"/>
@@ -8350,6 +8423,8 @@
     <mergeCell ref="F64:L64"/>
     <mergeCell ref="B65:E65"/>
     <mergeCell ref="F65:L65"/>
+    <mergeCell ref="B66:E66"/>
+    <mergeCell ref="F66:L66"/>
   </mergeCells>
   <conditionalFormatting sqref="D19:H19">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
